--- a/jogos_2024-08-28.xlsx
+++ b/jogos_2024-08-28.xlsx
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.74</v>
+        <v>6.65</v>
       </c>
       <c r="O10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
         <v>2.1</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45532.58333333334</v>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="N11" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.85</v>
       </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.38</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['58', '67']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45532.58333333334</v>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6.65</v>
+        <v>1.85</v>
       </c>
       <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2.1</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['58', '67']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.06</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45532.58333333334</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>11.72</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>4.25</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['1', '90+3']</t>
+          <t>['45+5', '73', '84']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['49', '53']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.71</v>
+        <v>4.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45532.625</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,81 +2191,81 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
+      <c r="N14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11.72</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>1.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
         <v>1.83</v>
@@ -2275,25 +2275,25 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['45+5', '73', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['49', '53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45532.625</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
         <v>2.6</v>
       </c>
       <c r="P15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AA15" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '90+3']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45532.625</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,65 +2475,65 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="M16" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.32</v>
+        <v>2.54</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['18', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45532.64583333334</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.83</v>
+        <v>2.16</v>
       </c>
       <c r="M17" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.25</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG17" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45532.64583333334</v>
@@ -2707,16 +2707,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2733,65 +2733,65 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N18" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="O18" t="n">
         <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="X18" t="n">
-        <v>2.93</v>
+        <v>3.34</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['18', '47']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45532.64583333334</v>
@@ -2836,19 +2836,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['26', '59']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['5', '84']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45532.66666666666</v>
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.72</v>
+        <v>3.24</v>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y20" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="Z20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['5', '84']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.53</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['26', '59']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45532.66666666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Memphis 901</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.25</v>
       </c>
-      <c r="S34" t="n">
+      <c r="X34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
+      <c r="Y34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['4', '6', '75']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>2.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['7', '56']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45532.91666666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Memphis 901</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="O35" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="P35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['7', '56']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['4', '6', '75']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45532.91666666666</v>

--- a/jogos_2024-08-28.xlsx
+++ b/jogos_2024-08-28.xlsx
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="N10" t="n">
-        <v>6.65</v>
+        <v>3.74</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.75</v>
+        <v>3.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="X10" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
         <v>2.1</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>3.35</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45532.58333333334</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,55 +1830,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>6.65</v>
       </c>
       <c r="O11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
         <v>2.1</v>
@@ -1888,25 +1888,25 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45532.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,81 +2062,81 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="n">
+      <c r="N13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11.72</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>1.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
         <v>1.83</v>
@@ -2146,25 +2146,25 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['45+5', '73', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['49', '53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45532.625</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
         <v>2.6</v>
       </c>
       <c r="P14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AA14" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '90+3']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45532.625</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>11.72</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>4.25</v>
+        <v>6.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['1', '90+3']</t>
+          <t>['45+5', '73', '84']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['49', '53']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.71</v>
+        <v>4.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45532.625</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N16" t="n">
-        <v>2.54</v>
+        <v>3.32</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>['18', '47']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG16" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45532.64583333334</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.52</v>
+        <v>2.54</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AJ17" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.39</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45532.64583333334</v>
@@ -2707,16 +2707,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2733,65 +2733,65 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="N18" t="n">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="O18" t="n">
         <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>3.34</v>
+        <v>2.93</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['18', '47']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45532.64583333334</v>
@@ -2826,35 +2826,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['26', '59']</t>
+          <t>['6', '57', '90+3']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45532.66666666666</v>
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['26', '59']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['5', '84']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45532.66666666666</v>
@@ -3084,26 +3084,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3112,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['5', '84']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['6', '57', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45532.66666666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>4.42</v>
       </c>
       <c r="N23" t="n">
-        <v>5.65</v>
+        <v>7.3</v>
       </c>
       <c r="O23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.3</v>
       </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
       <c r="Q23" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.28</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X23" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['45+6', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45532.6875</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.45</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X24" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+6', '77']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45532.6875</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Memphis 901</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="O34" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="P34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['7', '56']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['4', '6', '75']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45532.91666666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Memphis 901</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.25</v>
       </c>
-      <c r="S35" t="n">
+      <c r="X35" t="n">
         <v>3.6</v>
       </c>
-      <c r="T35" t="n">
+      <c r="Y35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['4', '6', '75']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>2.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['7', '56']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45532.91666666666</v>
